--- a/docs/Files/EV_model/ODYM_Tutorial6_FabricationYieldLossLL_V1.0.xlsx
+++ b/docs/Files/EV_model/ODYM_Tutorial6_FabricationYieldLossLL_V1.0.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F30670E-948E-4B95-8AE0-4AF7CB57D858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F14AA14-F899-4D73-9013-3E069599871B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -779,15 +779,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.81640625" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" customWidth="1"/>
-    <col min="4" max="4" width="31.453125" customWidth="1"/>
+    <col min="1" max="1" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
+    <col min="4" max="4" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>39</v>
       </c>
@@ -798,7 +798,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -812,7 +812,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>18</v>
       </c>
@@ -826,7 +826,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
@@ -840,7 +840,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
@@ -854,7 +854,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
@@ -868,7 +868,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -882,7 +882,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
@@ -896,7 +896,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -910,7 +910,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>25</v>
       </c>
@@ -924,7 +924,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
@@ -938,7 +938,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
@@ -952,7 +952,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>31</v>
       </c>
@@ -966,7 +966,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>34</v>
       </c>
@@ -980,7 +980,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>36</v>
       </c>
@@ -994,37 +994,37 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>2</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>10</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>58</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>62</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>64</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>66</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C27" s="8" t="s">
         <v>15</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E28" s="1" t="s">
         <v>16</v>
       </c>
@@ -1165,21 +1165,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.36328125" customWidth="1"/>
-    <col min="3" max="3" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.36328125" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>58</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -1266,10 +1266,10 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D4" s="1"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F29" s="1"/>
     </row>
   </sheetData>
@@ -1280,9 +1280,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:M3"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>68</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="13">
         <v>43344</v>
       </c>
@@ -1346,9 +1346,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:P3"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>82</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>100</v>
       </c>
